--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_yearly.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -890,12 +890,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -916,85 +916,89 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.100240007027905</v>
+        <v>5.031243764405162</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.3774670338474645</v>
+        <v>-0.6282614999612299</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.2902464771828115</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.08991080425787042</v>
+        <v>0.03472614880767842</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1643299012213698</v>
+        <v>0.1064221702798043</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9120988355580801</v>
+        <v>0.8111332007952287</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.08627628706692314</v>
+        <v>0.06641706281041238</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.3759620822245726</v>
+        <v>0.4072016674383538</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5269644188142332</v>
+        <v>0.5652818961713831</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.21463809261531</v>
+        <v>0.2288298671359227</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3663698603541443</v>
+        <v>0.4929366951175632</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>-0.144113255080112</v>
+        <v>-0.4889169376427428</v>
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
@@ -1028,7 +1032,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1059,51 +1063,51 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.031243764405162</v>
+        <v>10.37143903057632</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.6282614999612299</v>
+        <v>-0.2991160938550329</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2902464771828115</v>
+        <v>-0.4028865261537454</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.03472614880767842</v>
+        <v>0.09123209588906311</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1064221702798043</v>
+        <v>0.1662032077178436</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8111332007952287</v>
+        <v>0.9058506106219824</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.06641706281041238</v>
+        <v>0.09089426704839165</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.4072016674383538</v>
+        <v>0.3972461823630962</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5652818961713831</v>
+        <v>0.5563561428379309</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0.2288298671359227</v>
+        <v>0.2256076119401062</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.4929366951175632</v>
+        <v>0.4492652915769452</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
@@ -1115,39 +1119,39 @@
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>-0.4889169376427428</v>
+        <v>-0.03639280550137514</v>
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1165,7 +1169,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1183,68 +1187,64 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10.37143903057632</v>
+        <v>7.64155786772511</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2991160938550329</v>
+        <v>-0.4673735824267101</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4028865261537454</v>
+        <v>-0.3383158398603916</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.09123209588906311</v>
+        <v>0.07977656890840623</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1662032077178436</v>
+        <v>0.1503406989281701</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9058506106219824</v>
+        <v>0.8770235728486225</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.09089426704839165</v>
+        <v>0.08022995511302033</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.3972461823630962</v>
+        <v>0.3738126949134644</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5563561428379309</v>
+        <v>0.5239488661372884</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.2256076119401062</v>
+        <v>0.2371451338078873</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4492652915769452</v>
+        <v>0.5770731000279541</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
@@ -1256,67 +1256,47 @@
         </is>
       </c>
       <c r="Z6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0/6</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>-0.2677208829396426</v>
+      </c>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="AH6" s="2" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>1/6</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.03639280550137514</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0.1258582986804166</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AH6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AJ6" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AN6" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1326,7 +1306,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1357,51 +1337,51 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.64155786772511</v>
+        <v>10.09544040864768</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.4673735824267101</v>
+        <v>-0.3161273966204814</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3383158398603916</v>
+        <v>-0.4206716948626341</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.07977656890840623</v>
+        <v>0.09658003591659595</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1503406989281701</v>
+        <v>0.1693779859805054</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.8770235728486225</v>
+        <v>0.907980687304743</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.08022995511302033</v>
+        <v>0.08993550183991017</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.3738126949134644</v>
+        <v>0.3846092172413066</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5239488661372884</v>
+        <v>0.5394828297959942</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>0.2371451338078873</v>
+        <v>0.2137902381791522</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5770731000279541</v>
+        <v>0.432214450180106</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
@@ -1413,23 +1393,23 @@
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>-0.2677208829396426</v>
+        <v>-0.05978072123016065</v>
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
@@ -1463,7 +1443,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1481,68 +1461,64 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.09544040864768</v>
+        <v>4.571597429081829</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3161273966204814</v>
+        <v>-0.6565920145144359</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4206716948626341</v>
+        <v>-0.3150305412703731</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.09658003591659595</v>
+        <v>0.06785053980974015</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1693779859805054</v>
+        <v>0.121228644812698</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.907980687304743</v>
+        <v>0.7877023572848623</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.08993550183991017</v>
+        <v>0.06339618924816581</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.3846092172413066</v>
+        <v>0.33400462464123</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5394828297959942</v>
+        <v>0.4654169687211209</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0.2137902381791522</v>
+        <v>0.2012382323076302</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.432214450180106</v>
+        <v>0.6265926085933047</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
@@ -1554,33 +1530,31 @@
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.05978072123016065</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0.09853235179830366</v>
-      </c>
+        <v>-0.5278670225397855</v>
+      </c>
+      <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1591,30 +1565,12 @@
           <t>1/6</t>
         </is>
       </c>
-      <c r="AJ8" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AN8" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1624,7 +1580,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1655,51 +1611,51 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.571597429081829</v>
+        <v>9.743864681169393</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.6565920145144359</v>
+        <v>-0.3377969292555476</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3150305412703731</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.06785053980974015</v>
+        <v>0.0939972696722909</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.121228644812698</v>
+        <v>0.1674395028322885</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.7877023572848623</v>
+        <v>0.9094007384265833</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.06339618924816581</v>
+        <v>0.08868033135862396</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.33400462464123</v>
+        <v>0.3821791060143617</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.4654169687211209</v>
+        <v>0.5356496719626397</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>0.2012382323076302</v>
+        <v>0.2201124276982713</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.6265926085933047</v>
+        <v>0.4777270058094768</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
@@ -1711,39 +1667,39 @@
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>-0.5278670225397855</v>
+        <v>-0.08957298406498981</v>
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>1/6</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="AF9" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
       <c r="AH9" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1752,167 +1708,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>9.743864681169393</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.3377969292555476</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.0939972696722909</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1674395028322885</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9094007384265833</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>0.08868033135862396</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.3821791060143617</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.5356496719626397</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>0.2201124276982713</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.4777270058094768</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.08957298406498981</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0.0637237009906344</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1925,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2305,12 +2100,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2320,7 +2115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2331,68 +2126,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4355826533357545</v>
+        <v>0.3294967535274529</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.5835345717831015</v>
+        <v>0.4665154022251408</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.07939073608397251</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0881793893681919</v>
+        <v>0.02348245771646723</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1489104471765209</v>
+        <v>0.07753174524760817</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9462603878116344</v>
+        <v>0.7152354570637119</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1452528993287905</v>
+        <v>0.05616456569121109</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.6141277895968544</v>
+        <v>0.9944900363288223</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.3087473051992134</v>
+        <v>-0.119382527887404</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.07939073608397251</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.6795408281682738</v>
+        <v>0.2587969684983309</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.01895340505933174</v>
+        <v>-0.2647166064943113</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.9544262269956552</v>
+        <v>0.3634845824754631</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1145536846800933</v>
+        <v>-0.0777740138622881</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1234086346793246</v>
+        <v>0.04039159934147962</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1423643463039592</v>
+        <v>0.4115575738458714</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.01659340269675336</v>
+        <v>-0.2629478112558516</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2408,7 +2207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2439,62 +2238,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3294967535274529</v>
+        <v>0.3110190141621398</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.4665154022251408</v>
+        <v>0.4461333371274738</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.07939073608397251</v>
+        <v>-0.3149700650581952</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.02348245771646723</v>
+        <v>0.09650623120593957</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.07753174524760817</v>
+        <v>0.1488174561969029</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.7152354570637119</v>
+        <v>0.9518005540166204</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.05616456569121109</v>
+        <v>-0.2130100045473828</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.9944900363288223</v>
+        <v>0.4861734199475349</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.119382527887404</v>
+        <v>0.4527707549273073</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.07939073608397251</v>
+        <v>-0.3149700650581952</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2587969684983309</v>
+        <v>0.6658649051925247</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2647166064943113</v>
+        <v>-0.02694172986990617</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3634845824754631</v>
+        <v>0.9352181691051363</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.0777740138622881</v>
+        <v>-0.1145536846800933</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.04039159934147962</v>
+        <v>0.02593192897411134</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.4115575738458714</v>
+        <v>0.05180738372438087</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2629478112558516</v>
+        <v>-0.02460094419440795</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2510,7 +2309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2528,89 +2327,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.3110190141621398</v>
+        <v>0.2778810924357364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.4461333371274738</v>
+        <v>0.409580203409349</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3149700650581952</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.09650623120593957</v>
+        <v>0.1114259070568875</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1488174561969029</v>
+        <v>0.1527123066850303</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9518005540166204</v>
+        <v>0.9584487534626038</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2130100045473828</v>
+        <v>-0.2517736539689071</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.4861734199475349</v>
+        <v>0.412971084767529</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.4527707549273073</v>
+        <v>0.5351661656481069</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3149700650581952</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.6658649051925247</v>
+        <v>0.7078803749883373</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.02694172986990617</v>
+        <v>-0.002399823602007745</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9352181691051363</v>
+        <v>0.9942295848294278</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1145536846800933</v>
+        <v>-0.1157994371504594</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.02593192897411134</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.05180738372438087</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.02460094419440795</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.08676869902556683</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.07927152389915626</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.008142655865451154</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -2622,7 +2411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2653,7 +2442,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -2724,7 +2513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2742,89 +2531,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2778810924357364</v>
+        <v>0.1784558912595411</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.409580203409349</v>
+        <v>0.299908187658005</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.3031420059512167</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1114259070568875</v>
+        <v>0.111364098501702</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1527123066850303</v>
+        <v>0.1252274405727162</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9584487534626038</v>
+        <v>0.9728531855955679</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2517736539689071</v>
+        <v>-0.2069188776665427</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.412971084767529</v>
+        <v>0.4976760704515306</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5351661656481069</v>
+        <v>0.4398235503016085</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.3031420059512167</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.7078803749883373</v>
+        <v>0.4859209960668438</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.002399823602007745</v>
+        <v>-0.1320498382096074</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.9942295848294278</v>
+        <v>0.6824840004745149</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.0777740138622881</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0</v>
+        <v>-0.07780473610943217</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>0.05994813807385024</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.1098519549073534</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.1246225398793032</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.01687338964600871</v>
-      </c>
+        <v>-0.129961900243165</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -2836,7 +2615,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2867,180 +2646,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1784558912595411</v>
+        <v>0.2683441147140528</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.299908187658005</v>
+        <v>0.3990603396470505</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3031420059512167</v>
+        <v>-0.3250537462336849</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.111364098501702</v>
+        <v>0.1063867934015388</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1252274405727162</v>
+        <v>0.1500492735621578</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9728531855955679</v>
+        <v>0.9595567867036011</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2069188776665427</v>
+        <v>-0.2367770008029321</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4976760704515306</v>
+        <v>0.4412911745427819</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.4398235503016085</v>
+        <v>0.5032895127661476</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3031420059512167</v>
+        <v>-0.3250537462336849</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4859209960668438</v>
+        <v>0.6618263810817895</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1320498382096074</v>
+        <v>-0.02930069623796028</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6824840004745149</v>
+        <v>0.9295459958230248</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0777740138622881</v>
+        <v>-0.1153135073072581</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.07780473610943217</v>
+        <v>-0.007463118265178648</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.05994813807385024</v>
+        <v>0.02004293653320754</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.129961900243165</v>
+        <v>-0.02696558528395898</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.2683441147140528</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.3990603396470505</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.3250537462336849</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1063867934015388</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1500492735621578</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9595567867036011</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2367770008029321</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.4412911745427819</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.5032895127661476</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.3250537462336849</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.6618263810817895</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.02930069623796028</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.9295459958230248</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.1153135073072581</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.007463118265178648</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.02004293653320754</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.02696558528395898</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.1164952350413975</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.1070774050035036</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>-0.01054719646547908</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3053,7 +2720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3433,12 +3100,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3448,7 +3115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3459,68 +3126,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3499625568620768</v>
+        <v>0.04758133214067994</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.2815106712242617</v>
+        <v>-0.005537857854254202</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1399665328165783</v>
+        <v>0.03372190928387032</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1982343541210623</v>
+        <v>0.04075375809869702</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.936046511627907</v>
+        <v>0.9883720930232558</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.03465890935305149</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.2045306567846077</v>
+        <v>0.9443284617135477</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7983203326963466</v>
+        <v>0.06883470195705269</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.257317798460998</v>
+        <v>0.08519293573074371</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.0639087216303369</v>
+        <v>-0.4885318187085936</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.120882518504188</v>
+        <v>0.07594839783348827</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1172405796580748</v>
+        <v>-0.01464102629817676</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1272353726676549</v>
+        <v>-0.1252566766887556</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1183219266663929</v>
+        <v>0.8051721134106582</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.007970375782430095</v>
+        <v>-0.5154238663378634</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3536,7 +3207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3567,62 +3238,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.04758133214067994</v>
+        <v>0.3265612283821637</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.005537857854254202</v>
+        <v>0.2592959423672325</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.07484522873722499</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.03372190928387032</v>
+        <v>0.1407625494247685</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.04075375809869702</v>
+        <v>0.1982303538954557</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9883720930232558</v>
+        <v>0.938953488372093</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.03465890935305149</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.9443284617135477</v>
+        <v>0.2026678790745942</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.06883470195705269</v>
+        <v>0.8001571448140129</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.07484522873722499</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.08519293573074371</v>
+        <v>1.221623337080697</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.4885318187085936</v>
+        <v>0.04708537101382615</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.07594839783348827</v>
+        <v>1.089061368897005</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.01464102629817676</v>
+        <v>-0.1172405796580748</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1252566766887556</v>
+        <v>0.1076949749759668</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.8051721134106582</v>
+        <v>0.1165924686854938</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.5154238663378634</v>
+        <v>-0.007968434284713832</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -3638,7 +3309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3656,89 +3327,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.3265612283821637</v>
+        <v>0.4593757635217866</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.2592959423672325</v>
+        <v>0.3853759163709158</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1407625494247685</v>
+        <v>0.05168092594124149</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1982303538954557</v>
+        <v>0.1370268079008714</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.938953488372093</v>
+        <v>0.7361918604651163</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.2026678790745942</v>
+        <v>0.4910059614802476</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8001571448140129</v>
+        <v>0.5158382586150327</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.221623337080697</v>
+        <v>0.9714083440935686</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.04708537101382615</v>
+        <v>-0.07084481741740589</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.089061368897005</v>
+        <v>0.8659979462283562</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1172405796580748</v>
+        <v>-0.1247701957278803</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1076949749759668</v>
+        <v>0.218596748697599</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1165924686854938</v>
+        <v>0.3842940817834528</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.007968434284713832</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.0173347981845573</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.001546475965158223</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.01581277629788636</v>
-      </c>
+        <v>-0.1196980723000548</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -3750,7 +3411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3781,62 +3442,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4593757635217866</v>
+        <v>0.3062535046388968</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.3853759163709158</v>
+        <v>0.2400179523570771</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.05168092594124149</v>
+        <v>0.1445034556901349</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1370268079008714</v>
+        <v>0.2039921697445872</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.7361918604651163</v>
+        <v>0.9447674418604651</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.4206716948626341</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4910059614802476</v>
+        <v>0.1668461264815342</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5158382586150327</v>
+        <v>0.8354795715776951</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.9714083440935686</v>
+        <v>1.25477245467778</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.07084481741740589</v>
+        <v>0.06270906181621605</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.8659979462283562</v>
+        <v>1.118613377517173</v>
       </c>
       <c r="X7" s="2" t="n">
         <v>-0.1247701957278803</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.218596748697599</v>
+        <v>0.09073777536668004</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.3842940817834528</v>
+        <v>0.08333449293303352</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1196980723000548</v>
+        <v>0.006833791854631066</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3852,7 +3513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3870,89 +3531,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3062535046388968</v>
+        <v>0.4208299738324228</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.2400179523570771</v>
+        <v>0.3487846490305042</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.420671694862634</v>
+        <v>-0.1432282814604922</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1445034556901349</v>
+        <v>0.04301584881956443</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2039921697445872</v>
+        <v>0.1167663861705859</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9447674418604651</v>
+        <v>0.9222383720930233</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4206716948626341</v>
+        <v>-0.03465890935305183</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1668461264815342</v>
+        <v>0.944328461713547</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8354795715776951</v>
+        <v>0.06883470195705335</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.420671694862634</v>
+        <v>-0.07484522873722532</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.25477245467778</v>
+        <v>0.4718424270950872</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.06270906181621605</v>
+        <v>-0.3062979452341024</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.118613377517173</v>
+        <v>0.4206414071818901</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1247701957278804</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.09073777536668004</v>
+        <v>0.1864105392472741</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.08333449293303352</v>
+        <v>0.8051721134106575</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.006833791854631066</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.03237797374527152</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.03128565478247713</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>-0.001127596559489019</v>
-      </c>
+        <v>-0.3427715116838953</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -3964,7 +3615,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3995,180 +3646,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.4208299738324228</v>
+        <v>0.31498581851622</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.3487846490305042</v>
+        <v>0.2483074811009569</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1432282814604922</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.04301584881956443</v>
+        <v>0.140580955678969</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1167663861705859</v>
+        <v>0.2018606279812646</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9222383720930233</v>
+        <v>0.9404069767441861</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.03465890935305183</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.944328461713547</v>
+        <v>0.2026678790745942</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.06883470195705335</v>
+        <v>0.8001571448140129</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.07484522873722532</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4718424270950872</v>
+        <v>1.202237725512795</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.3062979452341024</v>
+        <v>0.03794863305194518</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.4206414071818901</v>
+        <v>1.07177934748319</v>
       </c>
       <c r="X9" s="2" t="n">
         <v>-0.1247701957278804</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1864105392472741</v>
+        <v>0.09802936507612792</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.8051721134106575</v>
+        <v>0.1165924686854938</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.3427715116838953</v>
+        <v>-0.01662477952338237</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.31498581851622</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.2483074811009569</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.140580955678969</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2018606279812646</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9404069767441861</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.2026678790745942</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.8001571448140129</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>1.202237725512795</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.03794863305194518</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>1.07177934748319</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.1247701957278804</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.09802936507612792</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.1165924686854938</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.01662477952338237</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.02590941368563482</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.001546475965158223</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>-0.02440067277445612</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4181,7 +3720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4561,12 +4100,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4576,7 +4115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4587,68 +4126,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.004205705299217932</v>
+        <v>0.0167853484502456</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.01876488188421255</v>
+        <v>-0.006472990324529415</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1465009124724217</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04678097528829382</v>
+        <v>0.04633586591900113</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1552469470901619</v>
+        <v>0.1676448275252701</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9517241379310345</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.138687252248779</v>
+        <v>-0.1464423397562968</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07053469759807562</v>
+        <v>0.06089581754970408</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7096268615961698</v>
+        <v>0.7493076420581823</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1465009124724217</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1659013615217844</v>
+        <v>0.1912321754103157</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08341586655962385</v>
+        <v>-0.06350181305251235</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.6099159566998359</v>
+        <v>0.7030415793294029</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02192041710993009</v>
+        <v>-0.02330447460112972</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.01237197523567835</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.009085604720955986</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.02126438020346932</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4664,7 +4207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4695,23 +4238,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0167853484502456</v>
+        <v>0.01678534845024493</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.006472990324529415</v>
+        <v>-0.006472990324530081</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1465009124724217</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.04633586591900113</v>
+        <v>0.04633586591900118</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1676448275252701</v>
+        <v>0.1676448275252702</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>0.9517241379310345</v>
@@ -4720,37 +4263,37 @@
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1464423397562968</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.06089581754970408</v>
+        <v>0.06089581754970363</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7493076420581823</v>
+        <v>0.7493076420581847</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1465009124724217</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1912321754103157</v>
+        <v>0.1912321754103152</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.06350181305251235</v>
+        <v>-0.06350181305251279</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7030415793294029</v>
+        <v>0.7030415793294013</v>
       </c>
       <c r="X5" s="2" t="n">
         <v>-0.02330447460112972</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -4766,7 +4309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4784,46 +4327,42 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.01678534845024493</v>
+        <v>-0.08026518742034072</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.006472990324530081</v>
+        <v>-0.1013035549445543</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1465009124724215</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.04633586591900118</v>
+        <v>0.06987044804855658</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1676448275252702</v>
+        <v>0.1476010707524129</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9931034482758621</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>-0.1464423397562973</v>
@@ -4835,38 +4374,32 @@
         <v>0.7493076420581847</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1465009124724215</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1912321754103152</v>
+        <v>0.07753096881241972</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.06350181305251279</v>
+        <v>-0.1528890677209772</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7030415793294013</v>
+        <v>0.285033073769457</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.0007985747912857555</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>-0.09544840119746734</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0.0125269584554677</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.009003799755391784</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.02172637816930578</v>
-      </c>
+        <v>-0.09544840119746734</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -4878,7 +4411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4909,23 +4442,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.08026518742034072</v>
+        <v>-0.001505251671993668</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1013035549445543</v>
+        <v>-0.02434520423114772</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1465009124724215</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.06987044804855658</v>
+        <v>0.04804912889692584</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1476010707524129</v>
+        <v>0.1652447026496686</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0.9931034482758621</v>
@@ -4943,28 +4476,28 @@
         <v>0.7493076420581847</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1465009124724215</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.07753096881241972</v>
+        <v>0.1698035116255907</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1528890677209772</v>
+        <v>-0.08034815518240823</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.285033073769457</v>
+        <v>0.6242617317550749</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.0007985747912857555</v>
+        <v>-0.0201533834440063</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.09544840119746734</v>
+        <v>-0.01798865429179974</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.09544840119746734</v>
+        <v>-0.01798865429179963</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4980,7 +4513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4998,40 +4531,36 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.001505251671993668</v>
+        <v>-0.08026518742034028</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.02434520423114772</v>
+        <v>-0.1013035549445539</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1465009124724218</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04804912889692584</v>
+        <v>0.06987044804855667</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1652447026496686</v>
+        <v>0.1476010707524129</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>0.9931034482758621</v>
@@ -5040,47 +4569,41 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.1464423397562969</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.06089581754970408</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.7493076420581829</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1465009124724218</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1698035116255907</v>
+        <v>0.07753096881241994</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.08034815518240823</v>
+        <v>-0.1528890677209771</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6242617317550749</v>
+        <v>0.2850330737694578</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0201533834440063</v>
+        <v>-0.0007985747912859775</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.01798865429179974</v>
+        <v>-0.095448401197467</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.01798865429179963</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.005687038961315172</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.009003799755391784</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.003346895571605835</v>
-      </c>
+        <v>-0.09544840119746711</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -5092,7 +4615,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5123,23 +4646,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.08026518742034028</v>
+        <v>-0.001505251671993668</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.1013035549445539</v>
+        <v>-0.02434520423114772</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1465009124724218</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.06987044804855667</v>
+        <v>0.04804912889692584</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1476010707524129</v>
+        <v>0.1652447026496686</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>0.9931034482758621</v>
@@ -5148,155 +4671,43 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1464423397562969</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.06089581754970408</v>
+        <v>0.06089581754970363</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7493076420581829</v>
+        <v>0.7493076420581847</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1465009124724218</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.07753096881241994</v>
+        <v>0.1698035116255907</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1528890677209771</v>
+        <v>-0.08034815518240823</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2850330737694578</v>
+        <v>0.6242617317550749</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0007985747912859775</v>
+        <v>-0.0201533834440063</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.095448401197467</v>
+        <v>-0.01798865429179974</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.09544840119746711</v>
+        <v>-0.01798865429179963</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.001505251671993668</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.02434520423114772</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.1465009124724216</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.04804912889692584</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1652447026496686</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9931034482758621</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.1464423397562973</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.06089581754970363</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7493076420581847</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.1465009124724216</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.1698035116255907</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.08034815518240823</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.6242617317550749</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.0201533834440063</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.01798865429179974</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.01798865429179963</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.005687038961315172</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.009003799755391784</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.003346895571605835</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5309,7 +4720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5689,12 +5100,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5704,7 +5115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5715,29 +5126,33 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.001560322013030691</v>
+        <v>0.003752373695924183</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08768794751503295</v>
+        <v>-0.08569122787067418</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1125125693043114</v>
+        <v>0.1177175505348944</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4092856064157859</v>
+        <v>0.4277127620168583</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>0.9918032786885246</v>
@@ -5746,37 +5161,37 @@
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.007998764021966531</v>
+        <v>-3.784557661234977e-05</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.9804376909420194</v>
+        <v>1.000092557658175</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3998874441902356</v>
+        <v>0.4142266877546181</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09492740958848467</v>
+        <v>-0.08565662401838869</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7314395722407911</v>
+        <v>0.7576676780024689</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.08260648781657542</v>
+        <v>-0.07121447292125138</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.002183857035198744</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.008036913760214537</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.01013928225831284</v>
+        <v>-3.33066907387547e-16</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5792,7 +5207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5823,20 +5238,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.003752373695924183</v>
+        <v>0.003752373695923961</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.08569122787067418</v>
+        <v>-0.0856912278706744</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1177175505348944</v>
+        <v>0.1177175505348945</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0.4277127620168583</v>
@@ -5848,37 +5263,37 @@
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-3.784557661234977e-05</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.000092557658175</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.4142266877546181</v>
+        <v>0.4142266877546186</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.08565662401838869</v>
+        <v>-0.08565662401838847</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7576676780024689</v>
+        <v>0.7576676780024697</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07121447292125138</v>
+        <v>-0.07121447292125116</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5894,7 +5309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5912,40 +5327,36 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>0.003752373695924183</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.08569122787067418</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>-0.2902464771828119</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.1177175505348944</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.4277127620168582</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>0.9918032786885246</v>
@@ -5966,35 +5377,29 @@
         <v>-0.2902464771828119</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.4142266877546188</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.08565662401838825</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.7576676780024701</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.07121447292125105</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0.002188636704864244</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.007972836758760149</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.01024314034952822</v>
-      </c>
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -6006,7 +5411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6037,23 +5442,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.003752373695924183</v>
+        <v>0.003752373695923961</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.08569122787067418</v>
+        <v>-0.0856912278706744</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>-0.2902464771828119</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1177175505348944</v>
+        <v>0.1177175505348945</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4277127620168582</v>
+        <v>0.4277127620168583</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>0.9918032786885246</v>
@@ -6074,25 +5479,25 @@
         <v>-0.2902464771828119</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.4142266877546188</v>
+        <v>0.4142266877546186</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.08565662401838825</v>
+        <v>-0.08565662401838847</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7576676780024701</v>
+        <v>0.7576676780024697</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.07121447292125105</v>
+        <v>-0.07121447292125116</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6108,7 +5513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6126,37 +5531,33 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>0.003752373695924627</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.08569122787067374</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.1177175505348944</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>0.4277127620168583</v>
@@ -6168,47 +5569,41 @@
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>-3.784557661279386e-05</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>1.000092557658176</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.4142266877546195</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.08565662401838781</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.7576676780024714</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.07121447292125149</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.002188636704864244</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.007972836758760149</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.01024314034952822</v>
-      </c>
+        <v>6.661338147750939e-16</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -6220,7 +5615,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6251,20 +5646,20 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.003752373695924627</v>
+        <v>0.003752373695923961</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.08569122787067374</v>
+        <v>-0.0856912278706744</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1177175505348944</v>
+        <v>0.1177175505348945</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0.4277127620168583</v>
@@ -6276,155 +5671,43 @@
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-3.784557661279386e-05</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>1.000092557658176</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4142266877546195</v>
+        <v>0.4142266877546186</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.08565662401838781</v>
+        <v>-0.08565662401838847</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7576676780024714</v>
+        <v>0.7576676780024697</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.07121447292125149</v>
+        <v>-0.07121447292125116</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.003752373695923961</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.0856912278706744</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1177175505348945</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.4277127620168583</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9918032786885246</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>1.000092557658176</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.4142266877546186</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.08565662401838847</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.7576676780024697</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.07121447292125116</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.002188636704864244</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.007972836758760149</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.01024314034952822</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6437,7 +5720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6817,12 +6100,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6832,7 +6115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6843,74 +6126,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.01404474995820859</v>
+        <v>0.1003269398943436</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.04427100028277864</v>
+        <v>0.03704926796423114</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.006696816304247677</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1240394247573673</v>
+        <v>0.0003872733026600608</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1633727596186971</v>
+        <v>0.01173672897439367</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9902534113060428</v>
+        <v>0.01559454191033138</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1179533974995302</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7372514143129777</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3142505667229638</v>
+        <v>0.0880281119184354</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1451083722677065</v>
+        <v>-0.2922611964811772</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.5848371626159791</v>
+        <v>0.1638250385406785</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.08922573857760219</v>
+        <v>-0.006696816304247677</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.07376306810835165</v>
+        <v>0.00504780378525238</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.0129429092318325</v>
+        <v>0.3276623824671059</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.08559808904327904</v>
+        <v>-0.2429944411638452</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.2383076748178463</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1920793993641633</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6920,7 +6211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6951,62 +6242,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.1003269398943436</v>
+        <v>0.02245251539292048</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.03704926796423114</v>
+        <v>-0.03634674915963509</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.006696816304247677</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0003872733026600608</v>
+        <v>0.1240399307850897</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.01173672897439367</v>
+        <v>0.163493029387094</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.01559454191033138</v>
+        <v>0.9902534113060428</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>0.1179533974995302</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>0.7372514143129777</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.0880281119184354</v>
+        <v>0.325147433442011</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2922611964811772</v>
+        <v>-0.1380201956577801</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.1638250385406785</v>
+        <v>0.6051168161416011</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.006696816304247677</v>
+        <v>-0.08922573857760219</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.00504780378525238</v>
+        <v>-0.06608334503830648</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.3276623824671059</v>
+        <v>0.0129429092318325</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2429944411638452</v>
+        <v>-0.0780164938713761</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -7015,7 +6306,7 @@
         <v>0.2383076748178463</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1920793993641633</v>
+        <v>-0.02819104197355771</v>
       </c>
     </row>
     <row r="6">
@@ -7026,7 +6317,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7044,95 +6335,81 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.02245251539292048</v>
+        <v>-0.09889493179083009</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.03634674915963509</v>
+        <v>-0.1507157396010765</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1240399307850897</v>
+        <v>0.1423071812985976</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.163493029387094</v>
+        <v>0.1492410538820038</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9902534113060428</v>
+        <v>1</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485824</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1179533974995302</v>
+        <v>0.1036687135184464</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7372514143129777</v>
+        <v>0.7690714431767565</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.325147433442011</v>
+        <v>0.1829910339693719</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1380201956577801</v>
+        <v>-0.2304898653043781</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.6051168161416011</v>
+        <v>0.3405561307552328</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.08922573857760219</v>
+        <v>-0.05302002584096688</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.06608334503830648</v>
+        <v>-0.1769231153511976</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.0129429092318325</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.0780164938713761</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0.008291315975018199</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.008291315975018421</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.2383076748178463</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.02819104197355771</v>
-      </c>
+        <v>-0.176923115351197</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7142,7 +6419,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7173,62 +6450,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.09889493179083009</v>
+        <v>0.02206741222589104</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1507157396010765</v>
+        <v>-0.03670970578914101</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1423071812985976</v>
+        <v>0.1246959777034307</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1492410538820038</v>
+        <v>0.1690989486582081</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9902534113060428</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2382824194485824</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1036687135184464</v>
+        <v>0.1036687135184475</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7690714431767565</v>
+        <v>0.769071443176754</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1829910339693719</v>
+        <v>0.3417931242784258</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2304898653043781</v>
+        <v>-0.12719253303835</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3405561307552328</v>
+        <v>0.6360953397448179</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.05302002584096688</v>
+        <v>-0.09255379523863527</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.1769231153511976</v>
+        <v>-0.06643510148288734</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.176923115351197</v>
+        <v>-0.06643510148288734</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7244,7 +6521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7262,89 +6539,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.02206741222589104</v>
+        <v>0.1003269398943438</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.03670970578914101</v>
+        <v>0.03704926796423136</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.006696816304248121</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1246959777034307</v>
+        <v>0.0003872733026600894</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1690989486582081</v>
+        <v>0.01173672897439369</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9902534113060428</v>
+        <v>0.01559454191033138</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1036687135184475</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.769071443176754</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.3417931242784258</v>
+        <v>0.08802811191843563</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.12719253303835</v>
+        <v>-0.292261196481177</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6360953397448179</v>
+        <v>0.1638250385406789</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.09255379523863527</v>
+        <v>-0.00669681630424801</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.06643510148288734</v>
+        <v>0.005047803785252603</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>0.3276623824671059</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.06643510148288734</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.007911546574264294</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.01277753081034727</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.02095685423529114</v>
-      </c>
+        <v>-0.2429944411638449</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -7356,7 +6623,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7387,180 +6654,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1003269398943438</v>
+        <v>0.02245251539292048</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.03704926796423136</v>
+        <v>-0.03634674915963509</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.006696816304248121</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.0003872733026600894</v>
+        <v>0.1240399307850897</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.01173672897439369</v>
+        <v>0.163493029387094</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.01559454191033138</v>
+        <v>0.9902534113060428</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>0.1179533974995302</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>0.7372514143129777</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.08802811191843563</v>
+        <v>0.325147433442011</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.292261196481177</v>
+        <v>-0.1380201956577801</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.1638250385406789</v>
+        <v>0.6051168161416011</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.00669681630424801</v>
+        <v>-0.08922573857760219</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.005047803785252603</v>
+        <v>-0.06608334503830648</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3276623824671059</v>
+        <v>0.0129429092318325</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2429944411638449</v>
+        <v>-0.0780164938713761</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.02245251539292048</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.03634674915963509</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1240399307850897</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.163493029387094</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9902534113060428</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1179533974995302</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7372514143129777</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.325147433442011</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1380201956577801</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.6051168161416011</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.08922573857760219</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.06608334503830648</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.0129429092318325</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.0780164938713761</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.008291315975018199</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.008291315975018421</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7573,7 +6728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7953,12 +7108,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7968,7 +7123,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7979,74 +7134,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>0.01733422320252154</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.2152266720452526</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.03198399714010958</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.03695724913837772</v>
+        <v>0.03916701675304846</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.03616236648452475</v>
+        <v>0.1910397615904498</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.07056771987481236</v>
+        <v>-0.1275127411654159</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.05707000491572423</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8056,7 +7219,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8087,62 +7250,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.05944967618015007</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>-0.05719067958884594</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.0679413098331703</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2181663348217244</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1277711346285673</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5578762400716401</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.07500868839622021</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.1640065156290161</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2623547528124305</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.04964464462786422</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.03916701675304846</v>
+        <v>-0.03695724913837772</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1910397615904498</v>
+        <v>0.03616236648452475</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1275127411654159</v>
+        <v>-0.07056771987481236</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -8151,7 +7314,7 @@
         <v>0.06587707306593171</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.05707000491572423</v>
+        <v>0.002524191693261901</v>
       </c>
     </row>
     <row r="6">
@@ -8162,7 +7325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8180,94 +7343,84 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>0.01733422320252154</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.2152266720452526</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.03198399714010958</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.03695724913837772</v>
+        <v>0.03916701675304846</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.03616236648452475</v>
+        <v>0.1910397615904498</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.07056771987481236</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.1275127411654159</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="n">
         <v>0.06587707306593171</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.002524191693261901</v>
+        <v>-0.05707000491572423</v>
       </c>
     </row>
     <row r="7">
@@ -8278,7 +7431,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8309,62 +7462,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.05944967618015007</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>-0.05719067958884594</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>0.0679413098331703</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2181663348217244</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1277711346285673</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5578762400716401</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.07500868839622021</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.1640065156290161</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2623547528124305</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.04964464462786422</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.03916701675304846</v>
+        <v>-0.03695724913837772</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1910397615904498</v>
+        <v>0.03616236648452475</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1275127411654159</v>
+        <v>-0.07056771987481236</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -8373,7 +7526,7 @@
         <v>0.06587707306593171</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.05707000491572423</v>
+        <v>0.002524191693261901</v>
       </c>
     </row>
     <row r="8">
@@ -8384,7 +7537,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8402,94 +7555,84 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>0.01733422320252154</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.2152266720452526</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.03198399714010958</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.03695724913837772</v>
+        <v>0.03916701675304846</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.03616236648452475</v>
+        <v>0.1910397615904498</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.07056771987481236</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.1275127411654159</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
         <v>0.06587707306593171</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.002524191693261901</v>
+        <v>-0.05707000491572423</v>
       </c>
     </row>
     <row r="9">
@@ -8500,7 +7643,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8531,62 +7674,62 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.05944967618015007</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>-0.05719067958884594</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>0.0679413098331703</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2181663348217244</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1277711346285673</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5578762400716401</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.07500868839622021</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.1640065156290161</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.2623547528124305</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.04964464462786422</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.03916701675304846</v>
+        <v>-0.03695724913837772</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1910397615904498</v>
+        <v>0.03616236648452475</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1275127411654159</v>
+        <v>-0.07056771987481236</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -8595,122 +7738,6 @@
         <v>0.06587707306593171</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.05707000491572423</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.05944967618015007</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.05719067958884594</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.0679413098331703</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2181663348217244</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1277711346285673</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.5578762400716401</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.07500868839622021</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1640065156290161</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.2623547528124305</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.04964464462786422</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.03695724913837772</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.03616236648452475</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.07056771987481236</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.06587707306593171</v>
-      </c>
-      <c r="AF10" s="2" t="n">
         <v>0.002524191693261901</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_yearly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>0.3840428795918789</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -966,19 +967,19 @@
         <v>0.4929366951175632</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
@@ -986,7 +987,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -994,27 +995,27 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1103,27 +1104,27 @@
         <v>0.4492652915769452</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1131,19 +1132,19 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1151,7 +1152,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1240,19 +1241,19 @@
         <v>0.5770731000279541</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
@@ -1260,7 +1261,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1268,27 +1269,27 @@
       </c>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr"/>
@@ -1377,27 +1378,27 @@
         <v>0.432214450180106</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1405,27 +1406,27 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1514,19 +1515,19 @@
         <v>0.6265926085933047</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
@@ -1534,7 +1535,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1542,27 +1543,27 @@
       </c>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr"/>
@@ -1651,27 +1652,27 @@
         <v>0.4777270058094768</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1679,19 +1680,19 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
@@ -1699,7 +1700,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1950,28 +1951,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196766684</v>
+        <v>0.05644008609220896</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208207</v>
+        <v>0.08831268540851259</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571159</v>
+        <v>0.2970580221997939</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798217</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -1980,10 +1981,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278889</v>
+        <v>0.2724034021441999</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -1992,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1395291740668931</v>
+        <v>-0.08310591627223018</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2038,49 +2039,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.2778810924357364</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.409580203409349</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1114259070568875</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1527123066850303</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9584487534626038</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2517736539689071</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.412971084767529</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.5351661656481069</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.7078803749883373</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.002399823602007745</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9942295848294278</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.05511881647811512</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2140,58 +2141,58 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3294967535274529</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4665154022251408</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.07939073608397251</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.02348245771646723</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.07753174524760817</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.7152354570637119</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.05616456569121109</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.9944900363288223</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.119382527887404</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.07939073608397251</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2587969684983309</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2647166064943113</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.3634845824754631</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.0777740138622881</v>
+        <v>-0.05511881647811512</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.04039159934147962</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.4115575738458714</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2629478112558516</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2242,58 +2243,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3110190141621398</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.4461333371274738</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3149700650581952</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.09650623120593957</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1488174561969029</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9518005540166204</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2130100045473828</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.4861734199475349</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.4527707549273073</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3149700650581952</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.6658649051925247</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.02694172986990617</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9352181691051363</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1145536846800933</v>
+        <v>-0.05511881647811512</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.02593192897411134</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.05180738372438087</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.02460094419440795</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2344,49 +2345,49 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.2778810924357364</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.409580203409349</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1114259070568875</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1527123066850303</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9584487534626038</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2517736539689071</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.412971084767529</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5351661656481069</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.7078803749883373</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.002399823602007745</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9942295848294278</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.05511881647811512</v>
       </c>
       <c r="Y6" s="2" t="n">
         <v>0</v>
@@ -2446,49 +2447,49 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.2778810924357364</v>
+        <v>0.05780006109971869</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.409580203409349</v>
+        <v>0.00128731863303333</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1114259070568875</v>
+        <v>0.08435250706252208</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1527123066850303</v>
+        <v>0.2776876941001362</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9584487534626038</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2517736539689071</v>
+        <v>-0.1629630992012946</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.412971084767529</v>
+        <v>0.008148606170506056</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5351661656481069</v>
+        <v>0.9601389978554115</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.7078803749883373</v>
+        <v>0.2637436415173093</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.002399823602007745</v>
+        <v>-0.00680582951310682</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.9942295848294278</v>
+        <v>0.9682097926871471</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1157994371504594</v>
+        <v>-0.05511881647811512</v>
       </c>
       <c r="Y7" s="2" t="n">
         <v>0</v>
@@ -2548,64 +2549,68 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1784558912595411</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.299908187658005</v>
+        <v>-0.03796582501302292</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3031420059512167</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.111364098501702</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1252274405727162</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9728531855955679</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2069188776665427</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.4976760704515306</v>
+        <v>0.2117597153840098</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.4398235503016085</v>
+        <v>-0.03587709265072057</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3031420059512167</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4859209960668438</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1320498382096074</v>
+        <v>-0.2060850325577082</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6824840004745149</v>
+        <v>0.03737143334716829</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0777740138622881</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.07780473610943217</v>
+        <v>-0.03920267730909144</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.05994813807385024</v>
+        <v>0.2019653729294226</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.129961900243165</v>
+        <v>-0.2006447570538082</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.2557598127090419</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.1821547032756365</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2650,64 +2655,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.2683441147140528</v>
+        <v>0.05457530154480672</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.3990603396470505</v>
+        <v>-0.001765158831013469</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3250537462336849</v>
+        <v>-0.1638829728650903</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1063867934015388</v>
+        <v>0.08632807107018843</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1500492735621578</v>
+        <v>0.2743481803517015</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9595567867036011</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2367770008029321</v>
+        <v>-0.1638829728650902</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4412911745427819</v>
+        <v>0.007040686852822775</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.5032895127661476</v>
+        <v>0.9655586700513813</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3250537462336849</v>
+        <v>-0.1638829728650903</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.6618263810817895</v>
+        <v>0.2612771505903662</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.02930069623796028</v>
+        <v>-0.00874427994697613</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.9295459958230248</v>
+        <v>0.9591552401098723</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1153135073072581</v>
+        <v>-0.0430164391150275</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.007463118265178648</v>
+        <v>-0.003048553004959542</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.02004293653320754</v>
+        <v>-0.001098964290484505</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.02696558528395898</v>
+        <v>-0.001951733600005889</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.2557598127090419</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.009700156822086914</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2950,28 +2959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.0534149946425504</v>
+        <v>-0.09123360655355228</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2216991067360385</v>
+        <v>0.2716992530341478</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389480542019929</v>
+        <v>0.1810585772249195</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.5035092528573141</v>
+        <v>-0.4707583434268607</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2980,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.121721302370637</v>
+        <v>0.717110477150922</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2992,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756414</v>
+        <v>-0.1395291740668931</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3038,49 +3047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1975871140978549</v>
+        <v>0.2834444878548723</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.1368616548924535</v>
+        <v>0.412293078958915</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1847647558521955</v>
+        <v>0.1114874581688012</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2118271660599822</v>
+        <v>0.1527921426208967</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9614825581395349</v>
+        <v>0.9584026622296173</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.2500855498878848</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.07708757922255405</v>
+        <v>0.4169603635659389</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9239869583598836</v>
+        <v>0.5312397610786888</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.239468393809461</v>
+        <v>0.711454536798154</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.05549602170052359</v>
+        <v>-0.003293870969882207</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.104970005642202</v>
+        <v>0.9921128744691625</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1157994371504594</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3140,58 +3149,58 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.04758133214067994</v>
+        <v>0.3352848633853369</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.005537857854254202</v>
+        <v>0.4693378551569682</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.07484522873722499</v>
+        <v>-0.07939073608397251</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.03372190928387032</v>
+        <v>0.02349453239066476</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.04075375809869702</v>
+        <v>0.07756494966748789</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9883720930232558</v>
+        <v>0.7149195784803106</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.03465890935305149</v>
+        <v>0.05854742179221817</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.9443284617135477</v>
+        <v>1.000121133030901</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.06883470195705269</v>
+        <v>-0.1243683146771766</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.07484522873722499</v>
+        <v>-0.07939073608397251</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.08519293573074371</v>
+        <v>0.2614313122831822</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.4885318187085936</v>
+        <v>-0.2653755660636441</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.07594839783348827</v>
+        <v>0.3645621150618912</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.01464102629817676</v>
+        <v>-0.0777740138622881</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.1252566766887556</v>
+        <v>0.04039159934147962</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.8051721134106582</v>
+        <v>0.4115575738458714</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.5154238663378634</v>
+        <v>-0.2629478112558515</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3242,58 +3251,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3265612283821637</v>
+        <v>0.3167266791561394</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.2592959423672325</v>
+        <v>0.4489165627731062</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.3149700650581954</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1407625494247685</v>
+        <v>0.09655948369859825</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1982303538954557</v>
+        <v>0.1488949416849816</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.938953488372093</v>
+        <v>0.9517470881863561</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.2112344442104684</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.2026678790745942</v>
+        <v>0.4903693728434375</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.8001571448140129</v>
+        <v>0.4487109939949196</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.3149700650581954</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1.221623337080697</v>
+        <v>0.6693511392471161</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.04708537101382615</v>
+        <v>-0.02781378282837665</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.089061368897005</v>
+        <v>0.9334003066116763</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1172405796580748</v>
+        <v>-0.1145536846800933</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.1076949749759668</v>
+        <v>0.02593192897411112</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1165924686854938</v>
+        <v>0.05180738372438065</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.007968434284713832</v>
+        <v>-0.02460094419440806</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -3344,58 +3353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.4593757635217866</v>
+        <v>0.2834444878548723</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.3853759163709158</v>
+        <v>0.412293078958915</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.05168092594124149</v>
+        <v>0.1114874581688012</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1370268079008714</v>
+        <v>0.1527921426208967</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.7361918604651163</v>
+        <v>0.9584026622296173</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.2500855498878848</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.4910059614802476</v>
+        <v>0.4169603635659389</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5158382586150327</v>
+        <v>0.5312397610786888</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.9714083440935686</v>
+        <v>0.711454536798154</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.07084481741740589</v>
+        <v>-0.003293870969882207</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.8659979462283562</v>
+        <v>0.9921128744691625</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1157994371504594</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.218596748697599</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.3842940817834528</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1196980723000548</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -3446,58 +3455,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3062535046388968</v>
+        <v>0.2834444878548723</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.2400179523570771</v>
+        <v>0.412293078958915</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.420671694862634</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1445034556901349</v>
+        <v>0.1114874581688012</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2039921697445872</v>
+        <v>0.1527921426208967</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9447674418604651</v>
+        <v>0.9584026622296173</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.4206716948626341</v>
+        <v>-0.2500855498878848</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1668461264815342</v>
+        <v>0.4169603635659389</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.8354795715776951</v>
+        <v>0.5312397610786888</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.420671694862634</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>1.25477245467778</v>
+        <v>0.711454536798154</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.06270906181621605</v>
+        <v>-0.003293870969882207</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.118613377517173</v>
+        <v>0.9921128744691625</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1247701957278803</v>
+        <v>-0.1157994371504594</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.09073777536668004</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.08333449293303352</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.006833791854631066</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3548,58 +3557,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.4208299738324228</v>
+        <v>0.1835864281662183</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.3487846490305042</v>
+        <v>0.3024099886413387</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1432282814604922</v>
+        <v>-0.3031420059512167</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04301584881956443</v>
+        <v>0.111425615251375</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1167663861705859</v>
+        <v>0.1252911849666572</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9222383720930233</v>
+        <v>0.9728230726566833</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.03465890935305183</v>
+        <v>-0.2051295748889884</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.944328461713547</v>
+        <v>0.5019044990861625</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.06883470195705335</v>
+        <v>0.4357428344142738</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.07484522873722532</v>
+        <v>-0.3031420059512167</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4718424270950872</v>
+        <v>0.48903065301608</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.3062979452341024</v>
+        <v>-0.1328276934826457</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.4206414071818901</v>
+        <v>0.6819460440168124</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1247701957278804</v>
+        <v>-0.0777740138622881</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1864105392472741</v>
+        <v>-0.0778047361094325</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.8051721134106575</v>
+        <v>0.05994813807385002</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.3427715116838953</v>
+        <v>-0.1299619002431651</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -3650,58 +3659,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.31498581851622</v>
+        <v>0.2738659898552198</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.2483074811009569</v>
+        <v>0.4017529686855512</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.3250537462336849</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.140580955678969</v>
+        <v>0.1064455426178543</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2018606279812646</v>
+        <v>0.1501275632069678</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9404069767441861</v>
+        <v>0.9595119245701609</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.2350550621589526</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.2026678790745942</v>
+        <v>0.4453604102029616</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.8001571448140129</v>
+        <v>0.4993115160697557</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.3250537462336849</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>1.202237725512795</v>
+        <v>0.6653041635265047</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.03794863305194518</v>
+        <v>-0.03017063509528861</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1.07177934748319</v>
+        <v>0.9277568585662788</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1247701957278804</v>
+        <v>-0.1153135073072581</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.09802936507612792</v>
+        <v>-0.007463118265178648</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1165924686854938</v>
+        <v>0.02004293653320732</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.01662477952338237</v>
+        <v>-0.02696558528395909</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -3950,28 +3959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.0534149946425504</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.08126757478702552</v>
+        <v>0.2216991067360385</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962864</v>
+        <v>0.2389480542019929</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573141</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3980,10 +3989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.121721302370637</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3992,7 +4001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756414</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4038,49 +4047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.01678534845024493</v>
+        <v>0.1975871140978549</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.006472990324530081</v>
+        <v>0.1368616548924535</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.04633586591900118</v>
+        <v>0.1847647558521955</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1676448275252702</v>
+        <v>0.2118271660599822</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9614825581395349</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.07708757922255405</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.9239869583598836</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.1912321754103152</v>
+        <v>1.239468393809461</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.06350181305251279</v>
+        <v>0.05549602170052359</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.7030415793294013</v>
+        <v>1.104970005642202</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.1247701957278803</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4140,58 +4149,58 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0167853484502456</v>
+        <v>0.04758133214067994</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.006472990324529415</v>
+        <v>-0.005537857854254202</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1465009124724217</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04633586591900113</v>
+        <v>0.03372190928387032</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1676448275252701</v>
+        <v>0.04075375809869702</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9883720930232558</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1464423397562968</v>
+        <v>-0.03465890935305149</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.06089581754970408</v>
+        <v>0.9443284617135477</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7493076420581823</v>
+        <v>0.06883470195705269</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1465009124724217</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1912321754103157</v>
+        <v>0.08519293573074371</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06350181305251235</v>
+        <v>-0.4885318187085936</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7030415793294029</v>
+        <v>0.07594839783348827</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.01464102629817676</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>-0.1252566766887556</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0.8051721134106582</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>-0.5154238663378634</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4242,58 +4251,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.01678534845024493</v>
+        <v>0.3265612283821637</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.006472990324530081</v>
+        <v>0.2592959423672325</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.04633586591900118</v>
+        <v>0.1407625494247685</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1676448275252702</v>
+        <v>0.1982303538954557</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.938953488372093</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.2026678790745942</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.8001571448140129</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1912321754103152</v>
+        <v>1.221623337080697</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.06350181305251279</v>
+        <v>0.04708537101382615</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7030415793294013</v>
+        <v>1.089061368897005</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02330447460112972</v>
+        <v>-0.1172405796580748</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0</v>
+        <v>0.1076949749759668</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.1165924686854938</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.007968434284713832</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -4344,58 +4353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.08026518742034072</v>
+        <v>0.4593757635217866</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1013035549445543</v>
+        <v>0.3853759163709158</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1465009124724215</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.06987044804855658</v>
+        <v>0.05168092594124149</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1476010707524129</v>
+        <v>0.1370268079008714</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9931034482758621</v>
+        <v>0.7361918604651163</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.4910059614802476</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.5158382586150327</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1465009124724215</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.07753096881241972</v>
+        <v>0.9714083440935686</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1528890677209772</v>
+        <v>-0.07084481741740589</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.285033073769457</v>
+        <v>0.8659979462283562</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.0007985747912857555</v>
+        <v>-0.1247701957278803</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.09544840119746734</v>
+        <v>0.218596748697599</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.3842940817834528</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.09544840119746734</v>
+        <v>-0.1196980723000548</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -4446,58 +4455,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.001505251671993668</v>
+        <v>0.3062535046388968</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.02434520423114772</v>
+        <v>0.2400179523570771</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.04804912889692584</v>
+        <v>0.1445034556901349</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1652447026496686</v>
+        <v>0.2039921697445872</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9931034482758621</v>
+        <v>0.9447674418604651</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4206716948626341</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.1668461264815342</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.8354795715776951</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1698035116255907</v>
+        <v>1.25477245467778</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.08034815518240823</v>
+        <v>0.06270906181621605</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6242617317550749</v>
+        <v>1.118613377517173</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.0201533834440063</v>
+        <v>-0.1247701957278803</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.01798865429179974</v>
+        <v>0.09073777536668004</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.08333449293303352</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.01798865429179963</v>
+        <v>0.006833791854631066</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4548,58 +4557,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.08026518742034028</v>
+        <v>0.4208299738324228</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1013035549445539</v>
+        <v>0.3487846490305042</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1465009124724218</v>
+        <v>-0.1432282814604922</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.06987044804855667</v>
+        <v>0.04301584881956443</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1476010707524129</v>
+        <v>0.1167663861705859</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9931034482758621</v>
+        <v>0.9222383720930233</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1464423397562969</v>
+        <v>-0.03465890935305183</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.06089581754970408</v>
+        <v>0.944328461713547</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7493076420581829</v>
+        <v>0.06883470195705335</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1465009124724218</v>
+        <v>-0.07484522873722532</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.07753096881241994</v>
+        <v>0.4718424270950872</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1528890677209771</v>
+        <v>-0.3062979452341024</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.2850330737694578</v>
+        <v>0.4206414071818901</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0007985747912859775</v>
+        <v>-0.1247701957278804</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.095448401197467</v>
+        <v>0.1864105392472741</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0.8051721134106575</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.09544840119746711</v>
+        <v>-0.3427715116838953</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -4650,58 +4659,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.001505251671993668</v>
+        <v>0.31498581851622</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.02434520423114772</v>
+        <v>0.2483074811009569</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.04804912889692584</v>
+        <v>0.140580955678969</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1652447026496686</v>
+        <v>0.2018606279812646</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9931034482758621</v>
+        <v>0.9404069767441861</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.06089581754970363</v>
+        <v>0.2026678790745942</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7493076420581847</v>
+        <v>0.8001571448140129</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1698035116255907</v>
+        <v>1.202237725512795</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.08034815518240823</v>
+        <v>0.03794863305194518</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6242617317550749</v>
+        <v>1.07177934748319</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.0201533834440063</v>
+        <v>-0.1247701957278804</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.01798865429179974</v>
+        <v>0.09802936507612792</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>0.1165924686854938</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.01798865429179963</v>
+        <v>-0.01662477952338237</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4950,28 +4959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.01891210187562642</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570336</v>
+        <v>0.08099293800751969</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886579</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4980,10 +4989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4992,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.05185156587886031</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5038,49 +5047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>0.01712918805183983</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.001749821030199383</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.04617799198161064</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.167065999353103</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.06593925421638414</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.7345409743619887</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.1912321754103152</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.06350181305251279</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.7030415793294013</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.02330447460112972</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5140,49 +5149,49 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.003752373695924183</v>
+        <v>0.01712918805184005</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08569122787067418</v>
+        <v>-0.001749821030199161</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.1465009124724217</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1177175505348944</v>
+        <v>0.04617799198161064</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.1670659993531029</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.146153697786501</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-3.784557661234977e-05</v>
+        <v>0.06593925421638436</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.000092557658175</v>
+        <v>0.7345409743619876</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.1465009124724217</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4142266877546181</v>
+        <v>0.1912321754103157</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08565662401838869</v>
+        <v>-0.06350181305251235</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7576676780024689</v>
+        <v>0.7030415793294029</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07121447292125138</v>
+        <v>-0.02330447460112972</v>
       </c>
       <c r="Y4" s="2" t="n">
         <v>2.220446049250313e-16</v>
@@ -5191,7 +5200,7 @@
         <v>2.220446049250313e-16</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-3.33066907387547e-16</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5242,49 +5251,49 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>0.01712918805183983</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.001749821030199383</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.04617799198161064</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.167065999353103</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.06593925421638414</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.7345409743619887</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.1912321754103152</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.06350181305251279</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.7030415793294013</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.02330447460112972</v>
       </c>
       <c r="Y5" s="2" t="n">
         <v>0</v>
@@ -5344,58 +5353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.003752373695924183</v>
+        <v>-0.07995416675898648</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.08569122787067418</v>
+        <v>-0.09703120460795256</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1177175505348944</v>
+        <v>0.06963238790827686</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4277127620168582</v>
+        <v>0.1470961345592113</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.06593925421638414</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.7345409743619887</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4142266877546188</v>
+        <v>0.07753096881241972</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08565662401838825</v>
+        <v>-0.1528890677209772</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7576676780024701</v>
+        <v>0.285033073769457</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.07121447292125105</v>
+        <v>-0.0007985747912857555</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.09544840119746745</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-0.09544840119746734</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -5446,58 +5455,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>-0.001167597282123678</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.01970699839641432</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.04788541758999994</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.1646745439789654</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.06593925421638414</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.7345409743619887</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.1698035116255907</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.08034815518240823</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.6242617317550749</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.0201533834440063</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0</v>
+        <v>-0.01798865429179974</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0</v>
+        <v>-0.01798865429179963</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5548,58 +5557,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.003752373695924627</v>
+        <v>-0.07995416675898637</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.08569122787067374</v>
+        <v>-0.09703120460795245</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1177175505348944</v>
+        <v>0.06963238790827669</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.1470961345592113</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.1461536977865011</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-3.784557661279386e-05</v>
+        <v>0.06593925421638436</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.7345409743619882</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4142266877546195</v>
+        <v>0.07753096881241994</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.08565662401838781</v>
+        <v>-0.1528890677209771</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7576676780024714</v>
+        <v>0.2850330737694578</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.07121447292125149</v>
+        <v>-0.0007985747912859775</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>-0.09544840119746734</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>-0.09544840119746711</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -5650,58 +5659,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.003752373695923961</v>
+        <v>-0.001167597282123678</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.0856912278706744</v>
+        <v>-0.01970699839641432</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.04788541758999994</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4277127620168583</v>
+        <v>0.1646745439789654</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9863013698630136</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.06593925421638414</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.7345409743619887</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4142266877546186</v>
+        <v>0.1698035116255907</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.08565662401838847</v>
+        <v>-0.08034815518240823</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7576676780024697</v>
+        <v>0.6242617317550749</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.07121447292125116</v>
+        <v>-0.0201533834440063</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0</v>
+        <v>-0.01798865429179974</v>
       </c>
       <c r="Z9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0</v>
+        <v>-0.01798865429179963</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5950,28 +5959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363057</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1799741913752893</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2405796270435321</v>
+        <v>0.4518304992174231</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450099</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5980,10 +5989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241682997</v>
+        <v>0.5657770181230004</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5992,7 +6001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174769</v>
+        <v>-0.05185156587886031</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6038,49 +6047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.09480060127513035</v>
+        <v>0.006687707983713542</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.03184073837926271</v>
+        <v>-0.09418218433661163</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1155318330023982</v>
+        <v>0.1158491063192834</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1720647483703307</v>
+        <v>0.4208473686607196</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.1036687135184475</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.769071443176754</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.4372788934221374</v>
+        <v>0.4183623971148742</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.06508110111248899</v>
+        <v>-0.09414790184163113</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.813799478447114</v>
+        <v>0.7394474920575899</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.08016850348153992</v>
+        <v>-0.07121447292125116</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6140,68 +6149,64 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.1003269398943436</v>
+        <v>0.006687707983713542</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.03704926796423114</v>
+        <v>-0.09418218433661163</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.006696816304247677</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0003872733026600608</v>
+        <v>0.1158491063192833</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.01173672897439367</v>
+        <v>0.4208473686607196</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.01559454191033138</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>-3.784557661234977e-05</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>1.000092557658175</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.0880281119184354</v>
+        <v>0.4183623971148738</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2922611964811772</v>
+        <v>-0.09414790184163147</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.1638250385406785</v>
+        <v>0.7394474920575891</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.006696816304247677</v>
+        <v>-0.07121447292125138</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.00504780378525238</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3276623824671059</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2429944411638452</v>
+        <v>-3.33066907387547e-16</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="n">
-        <v>0.2383076748178463</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>-0.1920793993641633</v>
-      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6246,68 +6251,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.02245251539292048</v>
+        <v>0.006687707983713542</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.03634674915963509</v>
+        <v>-0.09418218433661163</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1240399307850897</v>
+        <v>0.1158491063192834</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.163493029387094</v>
+        <v>0.4208473686607196</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9902534113060428</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1179533974995302</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7372514143129777</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.325147433442011</v>
+        <v>0.4183623971148742</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1380201956577801</v>
+        <v>-0.09414790184163113</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.6051168161416011</v>
+        <v>0.7394474920575899</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.08922573857760219</v>
+        <v>-0.07121447292125116</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.06608334503830648</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.0129429092318325</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.0780164938713761</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.2383076748178463</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.02819104197355771</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6352,58 +6353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.09889493179083009</v>
+        <v>0.006687707983713542</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1507157396010765</v>
+        <v>-0.09418218433661163</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1423071812985976</v>
+        <v>0.1158491063192833</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1492410538820038</v>
+        <v>0.4208473686607196</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2382824194485824</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1036687135184464</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7690714431767565</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1829910339693719</v>
+        <v>0.4183623971148742</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.2304898653043781</v>
+        <v>-0.09414790184163113</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.3405561307552328</v>
+        <v>0.7394474920575899</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.05302002584096688</v>
+        <v>-0.07121447292125105</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.1769231153511976</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.176923115351197</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -6454,58 +6455,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.02206741222589104</v>
+        <v>0.006687707983713542</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.03670970578914101</v>
+        <v>-0.09418218433661163</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1246959777034307</v>
+        <v>0.1158491063192834</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1690989486582081</v>
+        <v>0.4208473686607196</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9902534113060428</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1036687135184475</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.769071443176754</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.3417931242784258</v>
+        <v>0.4183623971148742</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.12719253303835</v>
+        <v>-0.09414790184163113</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6360953397448179</v>
+        <v>0.7394474920575899</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.09255379523863527</v>
+        <v>-0.07121447292125116</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.06643510148288734</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.06643510148288734</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6556,58 +6557,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1003269398943438</v>
+        <v>0.006687707983713986</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.03704926796423136</v>
+        <v>-0.09418218433661119</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.006696816304248121</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.0003872733026600894</v>
+        <v>0.1158491063192833</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.01173672897439369</v>
+        <v>0.4208473686607196</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.01559454191033138</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.4652994336443077</v>
+        <v>-3.784557661279386e-05</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.03648365119369596</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.08802811191843563</v>
+        <v>0.4183623971148751</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.292261196481177</v>
+        <v>-0.09414790184163058</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.1638250385406789</v>
+        <v>0.7394474920575914</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.00669681630424801</v>
+        <v>-0.07121447292125149</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.005047803785252603</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3276623824671059</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.2429944411638449</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -6658,58 +6659,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.02245251539292048</v>
+        <v>0.006687707983713542</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.03634674915963509</v>
+        <v>-0.09418218433661163</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1240399307850897</v>
+        <v>0.1158491063192834</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.163493029387094</v>
+        <v>0.4208473686607196</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9902534113060428</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1179533974995302</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7372514143129777</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.325147433442011</v>
+        <v>0.4183623971148742</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1380201956577801</v>
+        <v>-0.09414790184163113</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6051168161416011</v>
+        <v>0.7394474920575899</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.08922573857760219</v>
+        <v>-0.07121447292125116</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.06608334503830648</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.0129429092318325</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.0780164938713761</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -6958,28 +6959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003974677</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.103821015825279</v>
+        <v>0.1799741913752893</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213005</v>
+        <v>0.2405796270435321</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138072</v>
+        <v>-0.3098313187450099</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6988,10 +6989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922785</v>
+        <v>0.5373300241682997</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7000,7 +7001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174769</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7046,49 +7047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.02335558522365555</v>
+        <v>0.09480060127513035</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.02100989850384682</v>
+        <v>0.03184073837926271</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.07028481312061448</v>
+        <v>0.1155318330023982</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2368473235282732</v>
+        <v>0.1720647483703307</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.08841159562168954</v>
+        <v>0.1036687135184475</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.6940712220239806</v>
+        <v>0.769071443176754</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.1566293869752668</v>
+        <v>0.4372788934221374</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.1005331940285291</v>
+        <v>-0.06508110111248899</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.5478360571510722</v>
+        <v>0.813799478447114</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.04423229897254077</v>
+        <v>-0.08016850348153992</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7148,67 +7149,67 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1003269398943436</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>0.03704926796423114</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>-0.006696816304247677</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>0.0003872733026600608</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.01173672897439367</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0</v>
+        <v>0.01559454191033138</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.0880281119184354</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2922611964811772</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.1638250385406785</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0</v>
+        <v>-0.006696816304247677</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.03916701675304846</v>
+        <v>0.00504780378525238</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1910397615904498</v>
+        <v>0.3276623824671059</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1275127411654159</v>
+        <v>-0.2429944411638452</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
-        <v>0.06587707306593171</v>
+        <v>0.2383076748178463</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>-0.05707000491572423</v>
+        <v>-0.1920793993641633</v>
       </c>
     </row>
     <row r="5">
@@ -7254,67 +7255,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>0.02245251539292048</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>-0.03634674915963509</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0.1240399307850897</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>0.163493029387094</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.9902534113060428</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.1179533974995302</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>0.7372514143129777</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.325147433442011</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.1380201956577801</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.6051168161416011</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>-0.08922573857760219</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.03695724913837772</v>
+        <v>-0.06608334503830648</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.03616236648452475</v>
+        <v>0.0129429092318325</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.07056771987481236</v>
+        <v>-0.0780164938713761</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.06587707306593171</v>
+        <v>0.2383076748178463</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.002524191693261901</v>
+        <v>-0.02819104197355771</v>
       </c>
     </row>
     <row r="6">
@@ -7360,68 +7361,64 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.09889493179083009</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>-0.1507157396010765</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>0.1423071812985976</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1492410538820038</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2382824194485824</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1036687135184464</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.7690714431767565</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1829910339693719</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.2304898653043781</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.3405561307552328</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0</v>
+        <v>-0.05302002584096688</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.03916701675304846</v>
+        <v>-0.1769231153511976</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1910397615904498</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1275127411654159</v>
+        <v>-0.176923115351197</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="n">
-        <v>0.06587707306593171</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.05707000491572423</v>
-      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7466,68 +7463,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>0.02206741222589104</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>-0.03670970578914101</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0.1246959777034307</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>0.1690989486582081</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9902534113060428</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.1036687135184475</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>0.769071443176754</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.3417931242784258</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.12719253303835</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.6360953397448179</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>-0.09255379523863527</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.03695724913837772</v>
+        <v>-0.06643510148288734</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.03616236648452475</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.07056771987481236</v>
+        <v>-0.06643510148288734</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.06587707306593171</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>0.002524191693261901</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7572,68 +7565,64 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1003269398943438</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.01733422320252154</v>
+        <v>0.03704926796423136</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>-0.006696816304248121</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0</v>
+        <v>0.0003872733026600894</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.01173672897439369</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0</v>
+        <v>0.01559454191033138</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.4652994336443077</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.03648365119369596</v>
       </c>
       <c r="T8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.08802811191843563</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.2152266720452526</v>
+        <v>-0.292261196481177</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.03198399714010958</v>
+        <v>0.1638250385406789</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0</v>
+        <v>-0.00669681630424801</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.03916701675304846</v>
+        <v>0.005047803785252603</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1910397615904498</v>
+        <v>0.3276623824671059</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1275127411654159</v>
+        <v>-0.2429944411638449</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="n">
-        <v>0.06587707306593171</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>-0.05707000491572423</v>
-      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7678,68 +7667,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.05944967618015007</v>
+        <v>0.02245251539292048</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.05719067958884594</v>
+        <v>-0.03634674915963509</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.0679413098331703</v>
+        <v>0.1240399307850897</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2181663348217244</v>
+        <v>0.163493029387094</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.9902534113060428</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1277711346285673</v>
+        <v>0.1179533974995302</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.5578762400716401</v>
+        <v>0.7372514143129777</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.07500868839622021</v>
+        <v>0.325147433442011</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1640065156290161</v>
+        <v>-0.1380201956577801</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2623547528124305</v>
+        <v>0.6051168161416011</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.04964464462786422</v>
+        <v>-0.08922573857760219</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.03695724913837772</v>
+        <v>-0.06608334503830648</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.03616236648452475</v>
+        <v>0.0129429092318325</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.07056771987481236</v>
+        <v>-0.0780164938713761</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.06587707306593171</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>0.002524191693261901</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7752,7 +7737,1031 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947871</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138072</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490124</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.02027479846139824</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.02507631676042987</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.06992591782126945</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.2355679791479366</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.08841159562168954</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.6940712220239806</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.1602779293212004</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.1042692974226319</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.5426851908659128</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.04423229897254077</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>0.03607296000152194</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.1910397615904498</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.1301105190493336</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.05707000491572423</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>-0.05663389030906907</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>-0.06125721696357767</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.06782602895282974</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.2170118542583445</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.1277711346285673</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0.5578762400716401</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.07822701090317752</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.1676123335559584</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.2648689094166217</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>-0.04964464462786422</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>-0.0371115204452952</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.03616236648452475</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.07071660706846794</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>0.002524191693261901</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>0.03607296000152194</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.1910397615904498</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.1301105190493336</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.05707000491572423</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>-0.05663389030906907</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-0.06125721696357767</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.06782602895282974</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.2170118542583445</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.1277711346285673</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.5578762400716401</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.07822701090317752</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.1676123335559584</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.2648689094166217</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>-0.04964464462786422</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>-0.0371115204452952</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.03616236648452475</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.07071660706846794</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>0.002524191693261901</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.2208132840633975</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.03153481080418823</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>0.03607296000152194</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.1910397615904498</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.1301105190493336</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.05707000491572423</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>-0.05663389030906907</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.06125721696357767</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.06782602895282974</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.2170118542583445</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.1277711346285673</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.5578762400716401</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.07822701090317752</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.1676123335559584</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.2648689094166217</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>-0.04964464462786422</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>-0.0371115204452952</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.03616236648452475</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.07071660706846794</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>0.002524191693261901</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7858,12 +8867,8 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>563</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -7872,10 +8877,10 @@
       </c>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.5562326869806095</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -7906,10 +8911,10 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>963</v>
+        <v>563</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -7919,7 +8924,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.9149709302325582</v>
+        <v>0.5568496949528563</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -7952,8 +8957,12 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>963</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -7962,10 +8971,10 @@
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>0.9149709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8038,24 +9047,20 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-251</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>307</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -8086,21 +9091,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-251</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>307</v>
+      </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.9766081871345029</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -8117,30 +9124,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-30</v>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8170,15 +9179,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -8187,10 +9192,10 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="2" t="n">
-        <v>0.3655523255813953</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -8217,7 +9222,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr"/>
@@ -8226,16 +9231,14 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -8262,11 +9265,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -8275,10 +9282,10 @@
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>0.3655523255813953</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -8305,7 +9312,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
@@ -8317,13 +9324,13 @@
         <v>1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4873294346978557</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -8350,22 +9357,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-30</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -8385,37 +9390,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>-193</v>
-      </c>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>57</v>
+      </c>
       <c r="J14" s="2" t="n">
-        <v>0.2770083102493075</v>
+        <v>0.4873294346978557</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -8432,37 +9435,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>209</v>
-      </c>
+        <v>-30</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.3670058139534884</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -8489,25 +9490,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-134</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.5241379310344828</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -8534,11 +9537,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-193</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -8547,10 +9554,10 @@
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0</v>
+        <v>0.2773155851358846</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -8577,14 +9584,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8594,7 +9601,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.3670058139534884</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -8624,30 +9631,165 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-30</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>307</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
